--- a/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kamil sort de l'école. Papa l'attend près du portail. Maman arrivera plus tard. Papa montre un espace. C'est le carré de marelle. Papa dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Kamil prend une craie. Il saute dans les cases. Parce que papa le voit, Kamil reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Kamil pose un caillou. Le caillou est lisse. Il saute encore. Papa dit : je te vois. Kamil sourit. Il reste là. Les pieds restent dans le carré. Maman arrive. Elle voit Kamil aussi. Parce qu'il est dans l'espace montré, maman le trouve tout de suite.</t>
+          <t>Kamil sort de l'école. Papa l'attend près du portail. Maman arrivera plus tard. Papa montre un espace. C'est le carré de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Kamil prend une craie. Il saute dans les cases. Parce que papa le voit, Kamil reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Kamil pose un caillou. Le caillou est lisse. Il saute encore. Je te vois. Kamil sourit. Il reste là. Les pieds restent dans le carré. Maman arrive. Elle voit Kamil aussi. Parce qu'il est dans l'espace montré, maman le trouve tout de suite.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kamil sort de l'école. Papa l'attend près du portail. Maman arrivera plus tard. Papa montre un espace. C'est le carré de marelle.
+papa|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
+narrateur|Kamil prend une craie. Il saute dans les cases. Parce que papa le voit, Kamil reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Kamil pose un caillou. Le caillou est lisse. Il saute encore.
+papa|Je te vois.
+narrateur|Kamil sourit. Il reste là. Les pieds restent dans le carré. Maman arrive. Elle voit Kamil aussi. Parce qu'il est dans l'espace montré, maman le trouve tout de suite.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Kamil joue dans la cour. Où joue-t-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kamil est dans l'espace montré. Papa le voit. La marelle est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Kamil range la craie. Papa lui tend la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Kamil sourit. Il reste là. Les pieds restent dans le carré. Maman arrive. Elle voit Kamil aussi. Parce qu'il est dans l'espace montré, maman le trouve tout de suite.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Kamil joue dans la cour. Où joue-t-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Kamil est dans l'espace montré. Papa le voit. La marelle est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Kamil range la craie. Papa lui tend la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kamil joue où papa voit</t>
+          <t>La marelle d'Amir</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une craie ronde roule dans la poche d'Amir. Dans la cour, il joue à la marelle où papa voit. Maman le trouve tout de suite.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kamil sort de l'école. Papa l'attend près du portail. Maman arrivera plus tard. Papa montre un espace. C'est le carré de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Kamil prend une craie. Il saute dans les cases. Parce que papa le voit, Kamil reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Kamil pose un caillou. Le caillou est lisse. Il saute encore. Je te vois. Kamil sourit. Il reste là. Les pieds restent dans le carré. Maman arrive. Elle voit Kamil aussi. Parce qu'il est dans l'espace montré, maman le trouve tout de suite.</t>
+          <t>Une craie ronde roule dans une poche. Elle fait un petit bruit sec. Le portail de l'école est encore ouvert. Le muret est tiède. Une feuille est collée au grillage. Le grillage sent le fer chaud. Tu as entendu la craie, Amir ? Elle roule, papa. Oui. On la sort. Amir sort la craie. Elle est blanche et un peu cassée. Elle a un bout cassé. On peut encore dessiner. En ce moment, papa montre un espace. C'est le carré de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Amir prend la craie. Il trace un trait dans une case. Il saute dans les cases. Parce que papa le voit, Amir reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Amir pose un caillou. Le caillou est lisse. Il est lisse, papa. Oui. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Amir saute encore. Les pieds restent dans le carré. La craie laisse un trait blanc. Maman arrive près du portail. Elle voit Amir tout de suite. Je te vois, Amir. Tu es dans l'espace montré. Oui, maman. Bravo. Parce qu'il est dans l'espace montré, tu le trouves. Oui. L'adulte voit. Tu as fait du bon travail. Amir pose la craie. Un peu de blanc reste sur ses doigts. Le caillou lisse attend dans la case un.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kamil sort de l'école. Papa l'attend près du portail. Maman arrivera plus tard. Papa montre un espace. C'est le carré de marelle.
-papa|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
-narrateur|Kamil prend une craie. Il saute dans les cases. Parce que papa le voit, Kamil reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Kamil pose un caillou. Le caillou est lisse. Il saute encore.
+          <t>narrateur|Une craie ronde roule dans une poche.
+narrateur|Elle fait un petit bruit sec.
+narrateur|Le portail de l'école est encore ouvert.
+narrateur|Le muret est tiède.
+narrateur|Une feuille est collée au grillage.
+narrateur|Le grillage sent le fer chaud.
+papa|Tu as entendu la craie, Amir ?
+enfant-m|Elle roule, papa.
+papa|Oui.
+papa|On la sort.
+narrateur|Amir sort la craie.
+narrateur|Elle est blanche et un peu cassée.
+enfant-m|Elle a un bout cassé.
+papa|On peut encore dessiner.
+narrateur|En ce moment, papa montre un espace.
+narrateur|C'est le carré de marelle.
+papa|Tu joues ici.
+papa|C'est l'espace montré.
+papa|Ici, l'adulte voit.
+narrateur|Amir prend la craie.
+narrateur|Il trace un trait dans une case.
+narrateur|Il saute dans les cases.
+narrateur|Parce que papa le voit, Amir reste.
+narrateur|Il reste dans l'espace montré.
+narrateur|Papa s'assoit sur le muret.
+narrateur|L'adulte voit.
+narrateur|Amir pose un caillou.
+narrateur|Le caillou est lisse.
+enfant-m|Il est lisse, papa.
+papa|Oui.
 papa|Je te vois.
-narrateur|Kamil sourit. Il reste là. Les pieds restent dans le carré. Maman arrive. Elle voit Kamil aussi. Parce qu'il est dans l'espace montré, maman le trouve tout de suite.</t>
+papa|Tu restes dans l'espace montré ?
+enfant-m|Oui.
+papa|Bravo.
+narrateur|Amir saute encore.
+narrateur|Les pieds restent dans le carré.
+narrateur|La craie laisse un trait blanc.
+narrateur|Maman arrive près du portail.
+narrateur|Elle voit Amir tout de suite.
+maman|Je te vois, Amir.
+maman|Tu es dans l'espace montré.
+enfant-m|Oui, maman.
+maman|Bravo.
+papa|Parce qu'il est dans l'espace montré, tu le trouves.
+maman|Oui.
+maman|L'adulte voit.
+maman|Tu as fait du bon travail.
+narrateur|Amir pose la craie.
+narrateur|Un peu de blanc reste sur ses doigts.
+narrateur|Le caillou lisse attend dans la case un.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1405,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Kamil joue dans la cour. Où joue-t-il ?</t>
+          <t>Amir joue dans la cour. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Kamil joue dans la cour. Où joue-t-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir joue dans la cour.
+narrateur|Où joue-t-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kamil est dans l'espace montré. Papa le voit. La marelle est là.</t>
+          <t>Amir est dans l'espace montré. Papa le voit. Maman le voit aussi. L'adulte voit. La marelle est là. Tu as joué dans l'espace montré ? Oui. Bravo. On t'a vu tout de suite. La craie est un peu usée. Le caillou lisse est encore là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1733,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kamil est dans l'espace montré. Papa le voit. La marelle est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir est dans l'espace montré.
+narrateur|Papa le voit.
+narrateur|Maman le voit aussi.
+narrateur|L'adulte voit.
+narrateur|La marelle est là.
+papa|Tu as joué dans l'espace montré ?
+enfant-m|Oui.
+maman|Bravo.
+maman|On t'a vu tout de suite.
+narrateur|La craie est un peu usée.
+narrateur|Le caillou lisse est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Kamil range la craie. Papa lui tend la main.</t>
+          <t>Amir range la craie. Elle laisse un peu de blanc. Papa lui tend la main. Tu as fini la marelle ? Oui, maman. On rentre. Tu es resté où on voit. Dans l'espace montré. L'adulte voit. Bravo, Amir. Amir prend la main de papa. Maman ferme le sac. Le sac sent encore le goûter. La feuille au grillage bouge encore. Le portail fait un petit clic.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1910,23 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Kamil range la craie. Papa lui tend la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Amir range la craie.
+narrateur|Elle laisse un peu de blanc.
+narrateur|Papa lui tend la main.
+maman|Tu as fini la marelle ?
+enfant-m|Oui, maman.
+papa|On rentre.
+papa|Tu es resté où on voit.
+enfant-m|Dans l'espace montré.
+maman|L'adulte voit.
+papa|Bravo, Amir.
+narrateur|Amir prend la main de papa.
+narrateur|Maman ferme le sac.
+narrateur|Le sac sent encore le goûter.
+narrateur|La feuille au grillage bouge encore.
+narrateur|Le portail fait un petit clic.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1951,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La craie rentre dans la poche. J'ai joué à la marelle. Oui. Dans l'espace montré. Bravo, Amir. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2091,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La craie rentre dans la poche.
+enfant-m|J'ai joué à la marelle.
+papa|Oui.
+maman|Dans l'espace montré.
+papa|Bravo, Amir.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une craie ronde roule dans une poche. Elle fait un petit bruit sec. Le portail de l'école est encore ouvert. Le muret est tiède. Une feuille est collée au grillage. Le grillage sent le fer chaud. Tu as entendu la craie, Amir ? Elle roule, papa. Oui. On la sort. Amir sort la craie. Elle est blanche et un peu cassée. Elle a un bout cassé. On peut encore dessiner. En ce moment, papa montre un espace. C'est le carré de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Amir prend la craie. Il trace un trait dans une case. Il saute dans les cases. Parce que papa le voit, Amir reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Amir pose un caillou. Le caillou est lisse. Il est lisse, papa. Oui. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Amir saute encore. Les pieds restent dans le carré. La craie laisse un trait blanc. Maman arrive près du portail. Elle voit Amir tout de suite. Je te vois, Amir. Tu es dans l'espace montré. Oui, maman. Bravo. Parce qu'il est dans l'espace montré, tu le trouves. Oui. L'adulte voit. Tu as fait du bon travail. Amir pose la craie. Un peu de blanc reste sur ses doigts. Le caillou lisse attend dans la case un.</t>
+          <t>Une craie ronde roule dans une poche. Elle fait un petit bruit sec. Le portail de l'école est encore ouvert. Le muret est tiède. Une feuille est collée au grillage. Le grillage sent le fer chaud. Tu as entendu la craie, Amir ? Elle roule, papa. Oui. On la sort. Amir sort la craie. Elle est blanche et un peu cassée. Elle a un bout cassé. On peut encore dessiner. En ce moment, papa montre un espace. C'est le carré de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Amir prend la craie. Il trace un trait dans une case. Il saute dans les cases. Parce que papa le voit, Amir reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Amir pose un caillou. Le caillou est lisse. Il est lisse, papa. Oui. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Amir saute encore. Les pieds restent dans le carré. La craie laisse un trait blanc. Maman arrive près du portail. Elle voit Amir tout de suite. Je te vois, Amir. Tu es dans l'espace montré. Oui, maman. Bravo. Parce qu'il est dans l'espace montré, tu le trouves. Oui. L'adulte voit. Amir pose la craie. Un peu de blanc reste sur ses doigts. Le caillou lisse attend dans la case un.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kamil sort de l'école. Papa l'attend près du portail. Maman arrivera plus tard. Papa montre un &lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. C'est le carré de marelle. Papa dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Kamil prend une craie. Il saute dans les cases. Parce que papa le voit, Kamil reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Kamil pose un caillou. Le caillou est lisse. Il saute encore. Papa dit : je te vois. Kamil sourit. Il reste là. Les pieds restent dans le carré. Maman arrive. Elle voit Kamil aussi. Parce qu'il est dans l'espace montré, maman le trouve tout de suite.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une craie ronde roule dans une poche. Elle fait un petit bruit sec. Le portail de l'école est encore ouvert. Le muret est tiède. Une feuille est collée au grillage. Le grillage sent le fer chaud. Tu as entendu la craie, Amir ? Elle roule, papa. Oui. On la sort. Amir sort la craie. Elle est blanche et un peu cassée. Elle a un bout cassé. On peut encore dessiner. En ce moment, papa montre un espace. C'est le carré de marelle. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Amir prend la craie. Il trace un trait dans une case. Il saute dans les cases. Parce que papa le voit, Amir reste. Il reste dans l'espace montré. Papa s'assoit sur le muret. L'adulte voit. Amir pose un caillou. Le caillou est lisse. Il est lisse, papa. Oui. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Amir saute encore. Les pieds restent dans le carré. La craie laisse un trait blanc. Maman arrive près du portail. Elle voit Amir tout de suite. Je te vois, Amir. Tu es dans l'espace montré. Oui, maman. Bravo. Parce qu'il est dans l'espace montré, tu le trouves. Oui. L'adulte voit. Amir pose la craie. Un peu de blanc reste sur ses doigts. Le caillou lisse attend dans la case un.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1370,7 +1370,6 @@
 papa|Parce qu'il est dans l'espace montré, tu le trouves.
 maman|Oui.
 maman|L'adulte voit.
-maman|Tu as fait du bon travail.
 narrateur|Amir pose la craie.
 narrateur|Un peu de blanc reste sur ses doigts.
 narrateur|Le caillou lisse attend dans la case un.</t>
@@ -1410,7 +1409,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Kamil joue dans la cour. Où joue-t-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir joue dans la cour. Où joue-t-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1594,7 +1593,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kamil est dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Papa le voit. La marelle est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est dans l'espace montré. Papa le voit. Maman le voit aussi. L'adulte voit. La marelle est là. Tu as joué dans l'espace montré ? Oui. Bravo. On t'a vu tout de suite. La craie est un peu usée. Le caillou lisse est encore là.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1775,7 +1774,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kamil range la craie. Papa lui tend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir range la craie. Elle laisse un peu de blanc. Papa lui tend la main. Tu as fini la marelle ? Oui, maman. On rentre. Tu es resté où on voit. Dans l'espace montré. L'adulte voit. Bravo, Amir. Amir prend la main de papa. Maman ferme le sac. Le sac sent encore le goûter. La feuille au grillage bouge encore. Le portail fait un petit clic.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1951,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La craie rentre dans la poche. J'ai joué à la marelle. Oui. Dans l'espace montré. Bravo, Amir. L'histoire est finie.</t>
+          <t>La craie rentre dans la poche. J'ai joué à la marelle. Oui. Dans l'espace montré. Bravo, Amir.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La craie rentre dans la poche. J'ai joué à la marelle. Oui. Dans l'espace montré. Bravo, Amir.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2095,8 +2094,7 @@
 enfant-m|J'ai joué à la marelle.
 papa|Oui.
 maman|Dans l'espace montré.
-papa|Bravo, Amir.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Amir.</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2160,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour d'école</t>
+          <t>cour d'école, marelle</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kamil, papa, maman</t>
+          <t>Amir, papa, maman</t>
         </is>
       </c>
     </row>
